--- a/frontend/static/examples/已修習專業核心科目範本.xlsx
+++ b/frontend/static/examples/已修習專業核心科目範本.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Featured\good\frontend\static\examples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B41EC9AE-E3F4-401C-8649-38DD303BC975}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F55549C6-C4E7-44D4-9438-C37454984AD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>課程名稱</t>
   </si>
@@ -44,9 +44,6 @@
   <si>
     <t>成績
 (未修課科目不需填寫)</t>
-  </si>
-  <si>
-    <t>修課狀態(已修課為1、未修課為0)</t>
   </si>
   <si>
     <t>系統分析與設計</t>
@@ -146,7 +143,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="m/d"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -163,14 +160,6 @@
       <sz val="10"/>
       <color rgb="FF444444"/>
       <name val="Sans-serif"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
@@ -219,7 +208,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -227,16 +216,13 @@
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -245,7 +231,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -255,10 +241,7 @@
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="11">
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
+  <dxfs count="10">
     <dxf>
       <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -333,10 +316,10 @@
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="已修習專業核心科目-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="10"/>
-      <tableStyleElement type="headerRow" dxfId="9"/>
-      <tableStyleElement type="firstRowStripe" dxfId="8"/>
-      <tableStyleElement type="secondRowStripe" dxfId="7"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="9"/>
+      <tableStyleElement type="headerRow" dxfId="8"/>
+      <tableStyleElement type="firstRowStripe" dxfId="7"/>
+      <tableStyleElement type="secondRowStripe" dxfId="6"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -351,12 +334,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="已修習專業核心科目" displayName="已修習專業核心科目" ref="A1:D31" headerRowDxfId="6" dataDxfId="5" totalsRowDxfId="4">
-  <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="課程名稱" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="學分數" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="成績_x000a_(未修課科目不需填寫)" dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="修課狀態(已修課為1、未修課為0)" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="已修習專業核心科目" displayName="已修習專業核心科目" ref="A1:C31" headerRowDxfId="5" dataDxfId="4" totalsRowDxfId="3">
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="課程名稱" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="學分數" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="成績_x000a_(未修課科目不需填寫)" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="已修習專業核心科目-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -563,421 +545,297 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="23.5546875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.33203125" style="4" customWidth="1"/>
-    <col min="3" max="3" width="25" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.5546875" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.33203125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="25" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="38.25" customHeight="1">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="5" t="s">
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="22.5" customHeight="1">
+      <c r="A2" s="6" t="s">
         <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="22.5" customHeight="1">
-      <c r="A2" s="7" t="s">
-        <v>4</v>
       </c>
       <c r="B2" s="1">
         <v>3</v>
       </c>
       <c r="C2" s="1"/>
-      <c r="D2" s="3">
-        <f t="shared" ref="D2:D31" si="0">IF(ISBLANK(C2), 0, 1)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="22.5" customHeight="1">
-      <c r="A3" s="7" t="s">
+    </row>
+    <row r="3" spans="1:3" ht="22.5" customHeight="1">
+      <c r="A3" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1">
+        <v>2</v>
+      </c>
+      <c r="C3" s="1"/>
+    </row>
+    <row r="4" spans="1:3" ht="22.5" customHeight="1">
+      <c r="A4" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="1">
+        <v>2</v>
+      </c>
+      <c r="C4" s="1"/>
+    </row>
+    <row r="5" spans="1:3" ht="22.5" customHeight="1">
+      <c r="A5" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="1">
-        <v>2</v>
-      </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="22.5" customHeight="1">
-      <c r="A4" s="7" t="s">
+      <c r="B5" s="1">
+        <v>2</v>
+      </c>
+      <c r="C5" s="1"/>
+    </row>
+    <row r="6" spans="1:3" ht="22.5" customHeight="1">
+      <c r="A6" s="6" t="s">
         <v>7</v>
-      </c>
-      <c r="B4" s="1">
-        <v>2</v>
-      </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="3">
-        <f>IF(ISBLANK(C4), 0, 1)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="22.5" customHeight="1">
-      <c r="A5" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="1">
-        <v>2</v>
-      </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="22.5" customHeight="1">
-      <c r="A6" s="7" t="s">
-        <v>8</v>
       </c>
       <c r="B6" s="2">
         <v>45719</v>
       </c>
       <c r="C6" s="1"/>
-      <c r="D6" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="22.5" customHeight="1">
-      <c r="A7" s="7" t="s">
-        <v>9</v>
+    </row>
+    <row r="7" spans="1:3" ht="22.5" customHeight="1">
+      <c r="A7" s="6" t="s">
+        <v>8</v>
       </c>
       <c r="B7" s="2">
         <v>45719</v>
       </c>
       <c r="C7" s="1"/>
-      <c r="D7" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="22.5" customHeight="1">
-      <c r="A8" s="7" t="s">
-        <v>11</v>
+    </row>
+    <row r="8" spans="1:3" ht="22.5" customHeight="1">
+      <c r="A8" s="6" t="s">
+        <v>10</v>
       </c>
       <c r="B8" s="2">
         <v>45719</v>
       </c>
       <c r="C8" s="1"/>
-      <c r="D8" s="3">
-        <f>IF(ISBLANK(C8), 0, 1)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="22.5" customHeight="1">
-      <c r="A9" s="7" t="s">
-        <v>10</v>
+    </row>
+    <row r="9" spans="1:3" ht="22.5" customHeight="1">
+      <c r="A9" s="6" t="s">
+        <v>9</v>
       </c>
       <c r="B9" s="1">
         <v>2</v>
       </c>
       <c r="C9" s="1"/>
-      <c r="D9" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="22.5" customHeight="1">
-      <c r="A10" s="7" t="s">
+    </row>
+    <row r="10" spans="1:3" ht="22.5" customHeight="1">
+      <c r="A10" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="1">
+        <v>2</v>
+      </c>
+      <c r="C10" s="1"/>
+    </row>
+    <row r="11" spans="1:3" ht="22.5" customHeight="1">
+      <c r="A11" s="6" t="s">
         <v>12</v>
-      </c>
-      <c r="B10" s="1">
-        <v>2</v>
-      </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="3">
-        <f>IF(ISBLANK(C10), 0, 1)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="22.5" customHeight="1">
-      <c r="A11" s="7" t="s">
-        <v>13</v>
       </c>
       <c r="B11" s="2">
         <v>45690</v>
       </c>
       <c r="C11" s="1"/>
-      <c r="D11" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="22.5" customHeight="1">
-      <c r="A12" s="7" t="s">
+    </row>
+    <row r="12" spans="1:3" ht="22.5" customHeight="1">
+      <c r="A12" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="1">
+        <v>2</v>
+      </c>
+      <c r="C12" s="1"/>
+    </row>
+    <row r="13" spans="1:3" ht="22.5" customHeight="1">
+      <c r="A13" s="6" t="s">
         <v>14</v>
-      </c>
-      <c r="B12" s="1">
-        <v>2</v>
-      </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="22.5" customHeight="1">
-      <c r="A13" s="7" t="s">
-        <v>15</v>
       </c>
       <c r="B13" s="2">
         <v>45690</v>
       </c>
       <c r="C13" s="1"/>
-      <c r="D13" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="22.5" customHeight="1">
-      <c r="A14" s="7" t="s">
-        <v>16</v>
+    </row>
+    <row r="14" spans="1:3" ht="22.5" customHeight="1">
+      <c r="A14" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="B14" s="1">
         <v>3</v>
       </c>
       <c r="C14" s="1"/>
-      <c r="D14" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="22.5" customHeight="1">
-      <c r="A15" s="7" t="s">
+    </row>
+    <row r="15" spans="1:3" ht="22.5" customHeight="1">
+      <c r="A15" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="1">
+        <v>2</v>
+      </c>
+      <c r="C15" s="1"/>
+    </row>
+    <row r="16" spans="1:3" ht="22.5" customHeight="1">
+      <c r="A16" s="6" t="s">
         <v>17</v>
-      </c>
-      <c r="B15" s="1">
-        <v>2</v>
-      </c>
-      <c r="C15" s="1"/>
-      <c r="D15" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="22.5" customHeight="1">
-      <c r="A16" s="7" t="s">
-        <v>18</v>
       </c>
       <c r="B16" s="1">
         <v>3</v>
       </c>
       <c r="C16" s="1"/>
-      <c r="D16" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="22.5" customHeight="1">
-      <c r="A17" s="7" t="s">
+    </row>
+    <row r="17" spans="1:3" ht="22.5" customHeight="1">
+      <c r="A17" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" s="1">
+        <v>2</v>
+      </c>
+      <c r="C17" s="1"/>
+    </row>
+    <row r="18" spans="1:3" ht="22.5" customHeight="1">
+      <c r="A18" s="6" t="s">
         <v>19</v>
-      </c>
-      <c r="B17" s="1">
-        <v>2</v>
-      </c>
-      <c r="C17" s="1"/>
-      <c r="D17" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="22.5" customHeight="1">
-      <c r="A18" s="7" t="s">
-        <v>20</v>
       </c>
       <c r="B18" s="2">
         <v>45719</v>
       </c>
       <c r="C18" s="1"/>
-      <c r="D18" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="22.5" customHeight="1">
-      <c r="A19" s="7" t="s">
-        <v>21</v>
+    </row>
+    <row r="19" spans="1:3" ht="22.5" customHeight="1">
+      <c r="A19" s="6" t="s">
+        <v>20</v>
       </c>
       <c r="B19" s="1">
         <v>3</v>
       </c>
       <c r="C19" s="1"/>
-      <c r="D19" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="22.5" customHeight="1">
-      <c r="A20" s="7" t="s">
-        <v>22</v>
+    </row>
+    <row r="20" spans="1:3" ht="22.5" customHeight="1">
+      <c r="A20" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="B20" s="2">
         <v>45658</v>
       </c>
       <c r="C20" s="1"/>
-      <c r="D20" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="22.5" customHeight="1">
-      <c r="A21" s="7" t="s">
+    </row>
+    <row r="21" spans="1:3" ht="22.5" customHeight="1">
+      <c r="A21" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" s="1">
+        <v>2</v>
+      </c>
+      <c r="C21" s="1"/>
+    </row>
+    <row r="22" spans="1:3" ht="22.5" customHeight="1">
+      <c r="A22" s="6" t="s">
         <v>23</v>
-      </c>
-      <c r="B21" s="1">
-        <v>2</v>
-      </c>
-      <c r="C21" s="1"/>
-      <c r="D21" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="22.5" customHeight="1">
-      <c r="A22" s="7" t="s">
-        <v>24</v>
       </c>
       <c r="B22" s="2">
         <v>45719</v>
       </c>
       <c r="C22" s="1"/>
-      <c r="D22" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="22.5" customHeight="1">
-      <c r="A23" s="7" t="s">
+    </row>
+    <row r="23" spans="1:3" ht="22.5" customHeight="1">
+      <c r="A23" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" s="1">
+        <v>2</v>
+      </c>
+      <c r="C23" s="1"/>
+    </row>
+    <row r="24" spans="1:3" ht="22.5" customHeight="1">
+      <c r="A24" s="6" t="s">
         <v>25</v>
-      </c>
-      <c r="B23" s="1">
-        <v>2</v>
-      </c>
-      <c r="C23" s="1"/>
-      <c r="D23" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="22.5" customHeight="1">
-      <c r="A24" s="7" t="s">
-        <v>26</v>
       </c>
       <c r="B24" s="2">
         <v>45719</v>
       </c>
       <c r="C24" s="1"/>
-      <c r="D24" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="22.5" customHeight="1">
-      <c r="A25" s="7" t="s">
-        <v>27</v>
+    </row>
+    <row r="25" spans="1:3" ht="22.5" customHeight="1">
+      <c r="A25" s="6" t="s">
+        <v>26</v>
       </c>
       <c r="B25" s="2">
         <v>45690</v>
       </c>
       <c r="C25" s="1"/>
-      <c r="D25" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="22.5" customHeight="1">
-      <c r="A26" s="8" t="s">
-        <v>28</v>
+    </row>
+    <row r="26" spans="1:3" ht="22.5" customHeight="1">
+      <c r="A26" s="7" t="s">
+        <v>27</v>
       </c>
       <c r="B26" s="2">
         <v>45690</v>
       </c>
       <c r="C26" s="1"/>
-      <c r="D26" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="22.5" customHeight="1">
-      <c r="A27" s="7" t="s">
-        <v>29</v>
+    </row>
+    <row r="27" spans="1:3" ht="22.5" customHeight="1">
+      <c r="A27" s="6" t="s">
+        <v>28</v>
       </c>
       <c r="B27" s="2">
         <v>45690</v>
       </c>
       <c r="C27" s="1"/>
-      <c r="D27" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="22.5" customHeight="1">
-      <c r="A28" s="7" t="s">
-        <v>30</v>
+    </row>
+    <row r="28" spans="1:3" ht="22.5" customHeight="1">
+      <c r="A28" s="6" t="s">
+        <v>29</v>
       </c>
       <c r="B28" s="2">
         <v>45690</v>
       </c>
       <c r="C28" s="1"/>
-      <c r="D28" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="22.5" customHeight="1">
-      <c r="A29" s="7" t="s">
-        <v>31</v>
+    </row>
+    <row r="29" spans="1:3" ht="22.5" customHeight="1">
+      <c r="A29" s="6" t="s">
+        <v>30</v>
       </c>
       <c r="B29" s="2">
         <v>45690</v>
       </c>
       <c r="C29" s="1"/>
-      <c r="D29" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" ht="22.5" customHeight="1">
-      <c r="A30" s="7" t="s">
-        <v>32</v>
+    </row>
+    <row r="30" spans="1:3" ht="22.5" customHeight="1">
+      <c r="A30" s="6" t="s">
+        <v>31</v>
       </c>
       <c r="B30" s="1">
         <v>3</v>
       </c>
       <c r="C30" s="1"/>
-      <c r="D30" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" ht="22.5" customHeight="1">
-      <c r="A31" s="9" t="s">
-        <v>33</v>
+    </row>
+    <row r="31" spans="1:3" ht="22.5" customHeight="1">
+      <c r="A31" s="8" t="s">
+        <v>32</v>
       </c>
       <c r="B31" s="1">
         <v>3</v>
       </c>
       <c r="C31" s="1"/>
-      <c r="D31" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
